--- a/outputs/daily/hr_rankings_2026-07-22_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-22_remaining.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -17046,7 +17046,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -17326,7 +17326,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -17606,7 +17606,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -17886,7 +17886,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -18446,7 +18446,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -19006,7 +19006,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -19286,7 +19286,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -19566,7 +19566,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -19846,7 +19846,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -20126,7 +20126,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -20406,7 +20406,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -20686,7 +20686,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -21526,7 +21526,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
